--- a/request_forms/025_pos_setup_request_form--request_forms.xlsx
+++ b/request_forms/025_pos_setup_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -756,7 +756,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -815,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
